--- a/Documents/Gasoline Fueling Times Comparison.xlsx
+++ b/Documents/Gasoline Fueling Times Comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/sobel_aaron_epa_gov/Documents/Coding/RoadTripMetric/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A059AD72-EADA-4F47-BF85-5DA158A54CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A059AD72-EADA-4F47-BF85-5DA158A54CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D51B199E-E283-4941-BC74-425A24542EC0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{55FCA8EF-DDFF-46C7-AB19-B52D9C714C50}"/>
+    <workbookView xWindow="19090" yWindow="4630" windowWidth="19420" windowHeight="10300" xr2:uid="{55FCA8EF-DDFF-46C7-AB19-B52D9C714C50}"/>
   </bookViews>
   <sheets>
     <sheet name="Toyota RAV4" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="29">
   <si>
     <t>Vehicle</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>https://fueleconomy.gov/feg/Find.do?action=sbs&amp;id=48910</t>
+  </si>
+  <si>
+    <t>Highway Fuel Efficiency (MPG)*</t>
   </si>
 </sst>
 </file>
@@ -130,8 +133,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="175" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -269,10 +272,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -672,7 +675,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="B3" s="7">
         <v>35</v>
